--- a/excel-files/LAS PINAS/LAS PIÑAS CAA NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CAA NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A4AF127-6CD0-4D56-BCAE-51689770B20D}"/>
+  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEAEC381-92BB-40BE-98C4-C22D9363E410}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5480,7 +5480,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7181,7 +7181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7457,7 +7457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7540,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7816,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8879,7 +8879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9017,7 +9017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>23</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>23</v>
       </c>
@@ -12483,7 +12483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>23</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>23</v>
       </c>
@@ -12621,7 +12621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>23</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>23</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>23</v>
       </c>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12963,7 +12963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13025,7 +13025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13087,7 +13087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13149,7 +13149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13211,7 +13211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13273,7 +13273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13335,7 +13335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13397,7 +13397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13418,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5"/>
-      <c r="L121" s="1"/>
+      <c r="L121" s="32"/>
       <c r="M121" s="5"/>
       <c r="N121" s="5">
         <f t="shared" si="16"/>
@@ -13459,7 +13459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13521,7 +13521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13645,7 +13645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13707,7 +13707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13769,7 +13769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13790,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13828,190 +13828,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 D23:F31 D33:F41 H33:I41 D43:F51 H43:I51 D53:F61 H53:I61 D63:F71 H63:I71 D73:F81 H73:I81 D83:F91 H83:I91 D93:F101 H93:I101 D103:F110 H103:I110 D112:F127 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W63:X71 W73:X81 W83:X91 W93:X101 W103:X110 W112:X127 K6:L12 K112:K127 L112:L120 L122:L127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -14021,15 +13841,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F53:F61 F33:F41 F14:F21 F5:F12 F63:F71 F83:F91 F93:F101 F23:F31 F43:F51 F73:F81" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110 L5:L12 L112:L120 L122:L127" xr:uid="{401C9F81-9775-4FC9-A690-88763828F548}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14259,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14328,7 +14151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14397,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14466,7 +14289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14535,7 +14358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14604,7 +14427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14673,7 +14496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14812,7 +14635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14881,7 +14704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14950,7 +14773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15019,7 +14842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15088,7 +14911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15157,7 +14980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15226,7 +15049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15365,7 +15188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15434,7 +15257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15503,7 +15326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15572,7 +15395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15641,7 +15464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15710,7 +15533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15779,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15848,7 +15671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15987,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16056,7 +15879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16125,7 +15948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16194,7 +16017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16263,7 +16086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16332,7 +16155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16401,7 +16224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16470,7 +16293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16539,7 +16362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16608,7 +16431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16677,7 +16500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="43" spans="1:27" ht="19.149999999999999">
       <c r="A43" s="1">
         <v>5</v>
@@ -16747,7 +16570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16816,7 +16639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16885,7 +16708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16954,7 +16777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -17023,7 +16846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17092,7 +16915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17161,7 +16984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17230,7 +17053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17299,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17368,7 +17191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17507,7 +17330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17576,7 +17399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17645,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17714,7 +17537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17783,7 +17606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17852,7 +17675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17921,7 +17744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17990,7 +17813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18059,7 +17882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18128,7 +17951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -18197,7 +18020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
@@ -21479,7 +21302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -21548,7 +21371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -21617,7 +21440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21686,7 +21509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21755,7 +21578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21824,7 +21647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21893,7 +21716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -22667,12 +22490,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F103:F113 F67:F77 F79:F89 F115:F122 F3:F10 F55:F65 F91:F101 F12:F19 F21:F29 F43:F53 F31:F41" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113 X115:X122" xr:uid="{BC90966A-7C01-4379-917F-0574520AE40E}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
